--- a/dataset_t6_grouped/results2/G5/G5_T6588_W0053F0003T0006Z000C1N27_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6588_W0053F0003T0006Z000C1N27_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>21.73466395134236</v>
+        <v>3.531882892093134</v>
       </c>
       <c r="D2" t="n">
-        <v>22.97419752967312</v>
+        <v>3.733307098571883</v>
       </c>
       <c r="E2" t="n">
-        <v>7.139441516780985</v>
+        <v>1.16015924647691</v>
       </c>
       <c r="F2" t="n">
-        <v>7.111842455813619</v>
+        <v>1.155674399069713</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>7.455780917780393</v>
+        <v>1.211564399139314</v>
       </c>
       <c r="D3" t="n">
-        <v>8.750512618045885</v>
+        <v>1.421958300432456</v>
       </c>
       <c r="E3" t="n">
-        <v>7.139441516780985</v>
+        <v>1.16015924647691</v>
       </c>
       <c r="F3" t="n">
-        <v>7.111842455813619</v>
+        <v>1.155674399069713</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
